--- a/data/trans_dic/IP16A112_2023R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,54; 71,35</t>
+          <t>40,48; 71,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,89; 74,71</t>
+          <t>44,01; 75,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,03; 67,73</t>
+          <t>47,56; 69,78</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 63,89</t>
+          <t>29,73; 62,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,33; 63,71</t>
+          <t>27,73; 67,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,26; 59,4</t>
+          <t>34,82; 59,6</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,66; 75,7</t>
+          <t>25,07; 76,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 61,45</t>
+          <t>19,18; 59,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,7; 59,82</t>
+          <t>27,71; 58,25</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 49,65</t>
+          <t>9,99; 49,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 51,98</t>
+          <t>27,75; 52,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,65; 45,98</t>
+          <t>17,61; 45,83</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,06; 62,94</t>
+          <t>32,84; 64,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,49; 54,02</t>
+          <t>25,74; 53,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,63; 53,94</t>
+          <t>32,76; 53,1</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,78; 68,87</t>
+          <t>23,4; 68,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,02; 65,36</t>
+          <t>21,09; 69,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,59; 59,88</t>
+          <t>28,52; 60,69</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,13; 51,5</t>
+          <t>23,71; 51,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,35; 50,85</t>
+          <t>36,93; 50,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,9; 47,96</t>
+          <t>31,84; 48,35</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>14067</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33250</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10061; 17750</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14044; 24235</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26996; 39605</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11075</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10901</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21975</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6966; 14603</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6514; 15782</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16339; 27968</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4820</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6493</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2406; 7298</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3317; 10353</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7452; 15666</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>21887</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22467</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44354</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7724; 38141</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15497; 29548</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23458; 61039</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>14150</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13981</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28131</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9720; 19047</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9261; 19394</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>21479; 34816</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5517</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11934</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2860; 8331</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3227; 10607</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7848; 16701</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>79440</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>150957</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>41967; 90853</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>66408; 91666</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>113618; 172523</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A112_2023R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,48; 71,42</t>
+          <t>40,03; 71,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,01; 75,95</t>
+          <t>42,85; 75,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,56; 69,78</t>
+          <t>47,15; 69,03</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,73; 62,32</t>
+          <t>31,26; 65,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,73; 67,18</t>
+          <t>28,22; 65,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,82; 59,6</t>
+          <t>35,01; 59,65</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,07; 76,06</t>
+          <t>24,52; 75,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,18; 59,85</t>
+          <t>20,23; 62,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,71; 58,25</t>
+          <t>26,78; 60,57</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 49,32</t>
+          <t>10,22; 48,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,75; 52,91</t>
+          <t>27,96; 52,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,61; 45,83</t>
+          <t>16,9; 46,56</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,84; 64,36</t>
+          <t>32,36; 63,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,74; 53,91</t>
+          <t>26,08; 53,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,76; 53,1</t>
+          <t>33,02; 53,26</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,4; 68,17</t>
+          <t>22,46; 65,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,09; 69,33</t>
+          <t>21,62; 66,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,52; 60,69</t>
+          <t>27,12; 61,62</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,71; 51,32</t>
+          <t>24,85; 50,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,93; 50,98</t>
+          <t>37,67; 51,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,84; 48,35</t>
+          <t>32,72; 48,51</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10061; 17750</t>
+          <t>9948; 17806</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14044; 24235</t>
+          <t>13673; 23995</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26996; 39605</t>
+          <t>26764; 39183</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6966; 14603</t>
+          <t>7326; 15285</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6514; 15782</t>
+          <t>6630; 15354</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16339; 27968</t>
+          <t>16426; 27992</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2406; 7298</t>
+          <t>2353; 7268</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3317; 10353</t>
+          <t>3498; 10798</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7452; 15666</t>
+          <t>7202; 16290</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7724; 38141</t>
+          <t>7901; 37807</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15497; 29548</t>
+          <t>15613; 29088</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23458; 61039</t>
+          <t>22502; 62004</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9720; 19047</t>
+          <t>9578; 18720</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9261; 19394</t>
+          <t>9383; 19319</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21479; 34816</t>
+          <t>21654; 34924</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2860; 8331</t>
+          <t>2745; 8038</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3227; 10607</t>
+          <t>3308; 10215</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7848; 16701</t>
+          <t>7464; 16958</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>41967; 90853</t>
+          <t>43991; 89708</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66408; 91666</t>
+          <t>67734; 91701</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>113618; 172523</t>
+          <t>116757; 173112</t>
         </is>
       </c>
     </row>
